--- a/data/trans_orig/P23_1_2016_2023_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118626</t>
+          <t>121279</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161813</t>
+          <t>161871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51404</t>
+          <t>51590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180647</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237431</t>
+          <t>232355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>512987</t>
+          <t>512929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>556174</t>
+          <t>553521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>589598</t>
+          <t>589925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620326</t>
+          <t>620140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1109099</t>
+          <t>1114175</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1165883</t>
+          <t>1167398</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>191597</t>
+          <t>192244</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243800</t>
+          <t>244964</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>88115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>125851</t>
+          <t>127425</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>290926</t>
+          <t>289015</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357959</t>
+          <t>357194</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>777559</t>
+          <t>776395</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>829762</t>
+          <t>829115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>916134</t>
+          <t>914560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>954910</t>
+          <t>953870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1705385</t>
+          <t>1706150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1772418</t>
+          <t>1774329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,99%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122039</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>166596</t>
+          <t>168883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63641</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100595</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>200172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254949</t>
+          <t>255716</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>592092</t>
+          <t>589805</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636649</t>
+          <t>633981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682300</t>
+          <t>682711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>719254</t>
+          <t>718038</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286633</t>
+          <t>1285866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1343954</t>
+          <t>1341410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>178507</t>
+          <t>176598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230191</t>
+          <t>228469</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>112121</t>
+          <t>111200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160230</t>
+          <t>158086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>302977</t>
+          <t>303266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>371689</t>
+          <t>374477</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>707376</t>
+          <t>709098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>759060</t>
+          <t>760969</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>882264</t>
+          <t>884408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>930373</t>
+          <t>931294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1608372</t>
+          <t>1605584</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1677084</t>
+          <t>1676795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,68%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>657993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>752570</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1034000</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1154938</t>
+          <t>1154919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2639844</t>
+          <t>2639685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2735252</t>
+          <t>2734421</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3114697</t>
+          <t>3111801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3187471</t>
+          <t>3187553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5776579</t>
+          <t>5776598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5897517</t>
+          <t>5905661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023</t>
+          <t>Población que no fuma pero ha fumado (prevalencia exfumadores) en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133572</t>
+          <t>134948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>61049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142251</t>
+          <t>142116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>186371</t>
+          <t>185445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>500840</t>
+          <t>499464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>537508</t>
+          <t>535414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>615700</t>
+          <t>614703</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636460</t>
+          <t>636285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1123793</t>
+          <t>1124719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1167913</t>
+          <t>1168048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>187668</t>
+          <t>186900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>756146</t>
+          <t>831397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70487</t>
+          <t>70309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98636</t>
+          <t>98682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263588</t>
+          <t>265838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1024466</t>
+          <t>1015381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435715</t>
+          <t>360464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1004193</t>
+          <t>1004961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>859470</t>
+          <t>859424</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>887619</t>
+          <t>887797</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1125501</t>
+          <t>1134586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1886379</t>
+          <t>1884129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122679</t>
+          <t>121139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168695</t>
+          <t>164211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>37064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103313</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145092</t>
+          <t>140102</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259315</t>
+          <t>257652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>535821</t>
+          <t>540305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>581837</t>
+          <t>583377</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>830053</t>
+          <t>830863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>894844</t>
+          <t>896302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1378566</t>
+          <t>1380229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1492789</t>
+          <t>1497779</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170824</t>
+          <t>169963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218165</t>
+          <t>220390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103726</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152637</t>
+          <t>153266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>283166</t>
+          <t>285683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361147</t>
+          <t>357158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>708666</t>
+          <t>706441</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>756007</t>
+          <t>756868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>938389</t>
+          <t>937760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>987300</t>
+          <t>985999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1656711</t>
+          <t>1660700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1734692</t>
+          <t>1732175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>637003</t>
+          <t>641386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1404653</t>
+          <t>1477012</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261388</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>377059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>950224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1975074</t>
+          <t>1829952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2052967</t>
+          <t>1980608</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2820617</t>
+          <t>2816234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3281985</t>
+          <t>3281192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3396863</t>
+          <t>3382553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5140797</t>
+          <t>5285919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6168902</t>
+          <t>6165647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023_R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023_R2-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121279</t>
+          <t>119436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161871</t>
+          <t>161271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51590</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81805</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>178625</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232355</t>
+          <t>233278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>512929</t>
+          <t>513529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>553521</t>
+          <t>555364</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>589925</t>
+          <t>589896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>620140</t>
+          <t>621515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1114175</t>
+          <t>1113252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1167398</t>
+          <t>1167905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192244</t>
+          <t>193252</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>244964</t>
+          <t>245888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88115</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127425</t>
+          <t>124821</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289015</t>
+          <t>290347</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357194</t>
+          <t>357304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>776395</t>
+          <t>775471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>829115</t>
+          <t>828107</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>914560</t>
+          <t>917164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>953870</t>
+          <t>956633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1706150</t>
+          <t>1706040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1774329</t>
+          <t>1772997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>123574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168883</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64857</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100184</t>
+          <t>102516</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200172</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>255716</t>
+          <t>257459</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589805</t>
+          <t>589700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633981</t>
+          <t>635114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>682711</t>
+          <t>680379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>718038</t>
+          <t>718253</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1285866</t>
+          <t>1284123</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1341410</t>
+          <t>1341538</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176598</t>
+          <t>178806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228469</t>
+          <t>230001</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111200</t>
+          <t>113304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158086</t>
+          <t>160213</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303266</t>
+          <t>304940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374477</t>
+          <t>371420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>709098</t>
+          <t>707566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>760969</t>
+          <t>758761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884408</t>
+          <t>882281</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>931294</t>
+          <t>929190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1605584</t>
+          <t>1608641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1676795</t>
+          <t>1675121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>657993</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>752729</t>
+          <t>749469</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1025856</t>
+          <t>1030338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1154919</t>
+          <t>1155140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2639685</t>
+          <t>2642945</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2734421</t>
+          <t>2740250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3111801</t>
+          <t>3110195</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3187553</t>
+          <t>3188183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5776598</t>
+          <t>5776377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5905661</t>
+          <t>5901179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,14%</t>
         </is>
       </c>
     </row>
@@ -2673,32 +2673,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98998</t>
+          <t>104524</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134948</t>
+          <t>141248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2708,32 +2708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>65448</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2743,22 +2743,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142116</t>
+          <t>154336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>185445</t>
+          <t>199421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -2786,32 +2786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>519900</t>
+          <t>566801</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>499464</t>
+          <t>548380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>535414</t>
+          <t>585104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2821,32 +2821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>626568</t>
+          <t>680257</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>614703</t>
+          <t>667665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636285</t>
+          <t>690176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2856,27 +2856,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1146468</t>
+          <t>1247059</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1124719</t>
+          <t>1223320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1168048</t>
+          <t>1268405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>401011</t>
+          <t>173283</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>186900</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>831397</t>
+          <t>195091</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98682</t>
+          <t>105892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>484375</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>265838</t>
+          <t>235953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1015381</t>
+          <t>294857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -3129,32 +3129,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>790850</t>
+          <t>874493</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360464</t>
+          <t>852685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1004961</t>
+          <t>898028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3164,32 +3164,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>874742</t>
+          <t>980777</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>859424</t>
+          <t>964946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>887797</t>
+          <t>995414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3199,32 +3199,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1665592</t>
+          <t>1855269</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134586</t>
+          <t>1823757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1884129</t>
+          <t>1882661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3312,17 +3312,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3359,32 +3359,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>142209</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121139</t>
+          <t>143290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164211</t>
+          <t>190221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3394,32 +3394,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102503</t>
+          <t>98778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3429,32 +3429,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>217060</t>
+          <t>249051</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140102</t>
+          <t>223859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257652</t>
+          <t>280317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -3472,32 +3472,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>562307</t>
+          <t>636454</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>540305</t>
+          <t>611674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>583377</t>
+          <t>658605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>858515</t>
+          <t>728648</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>830863</t>
+          <t>713481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>896302</t>
+          <t>743848</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1420821</t>
+          <t>1365103</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1380229</t>
+          <t>1333837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1497779</t>
+          <t>1390295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>86,13%</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3585,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3620,17 +3620,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169963</t>
+          <t>178660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220390</t>
+          <t>227435</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3737,32 +3737,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>130637</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105027</t>
+          <t>121047</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153266</t>
+          <t>160999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3772,32 +3772,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>325343</t>
+          <t>341873</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>285683</t>
+          <t>309901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357158</t>
+          <t>367854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -3815,32 +3815,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>732125</t>
+          <t>788205</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>706441</t>
+          <t>762627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>756868</t>
+          <t>811402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3850,32 +3850,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>960389</t>
+          <t>975155</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>937760</t>
+          <t>954171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>985999</t>
+          <t>994123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3885,32 +3885,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1692515</t>
+          <t>1763359</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1660700</t>
+          <t>1737378</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1732175</t>
+          <t>1795331</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -3928,17 +3928,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3998,17 +3998,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4045,32 +4045,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>852438</t>
+          <t>663408</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>641386</t>
+          <t>618433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1477012</t>
+          <t>708368</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>338037</t>
+          <t>366543</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>337336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>377059</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4115,32 +4115,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1190474</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>950224</t>
+          <t>976529</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1829952</t>
+          <t>1084078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -4158,32 +4158,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2605182</t>
+          <t>2865953</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1980608</t>
+          <t>2820993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2816234</t>
+          <t>2910928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3320214</t>
+          <t>3364837</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3281192</t>
+          <t>3333063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3382553</t>
+          <t>3394044</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4228,32 +4228,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5925397</t>
+          <t>6230789</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5285919</t>
+          <t>6176662</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6165647</t>
+          <t>6284211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4306,17 +4306,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
